--- a/src/data/02_DANH_SACH_HOC_SINH.xlsx
+++ b/src/data/02_DANH_SACH_HOC_SINH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DuAn\EDUTEAM_BO_DU_LIEU_DAU_VAO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DuAn\eduteam_21_9_V2\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFE5B3C-EE4B-401A-99AE-1F26B52FECBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92586F90-E1E0-43A4-920B-90A5906F8CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13770" yWindow="3825" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7860" uniqueCount="3496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7866" uniqueCount="3502">
   <si>
     <t>Student_ID</t>
   </si>
@@ -10474,9 +10474,6 @@
     <t>4846711833</t>
   </si>
   <si>
-    <t>Group_ID</t>
-  </si>
-  <si>
     <t>1A</t>
   </si>
   <si>
@@ -10508,6 +10505,27 @@
   </si>
   <si>
     <t>5B</t>
+  </si>
+  <si>
+    <t>N5B</t>
+  </si>
+  <si>
+    <t>N6B</t>
+  </si>
+  <si>
+    <t>Group_ID1</t>
+  </si>
+  <si>
+    <t>Group_ID2</t>
+  </si>
+  <si>
+    <t>N4A</t>
+  </si>
+  <si>
+    <t>N2B</t>
+  </si>
+  <si>
+    <t>N3B</t>
   </si>
 </sst>
 </file>
@@ -10873,17 +10891,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1437"/>
+  <dimension ref="A1:H1437"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="7" max="8" width="10.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10903,10 +10921,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>3484</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3497</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3498</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -10926,10 +10947,10 @@
         <v>10</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>3485</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3484</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -10949,10 +10970,10 @@
         <v>10</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>3486</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3485</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -10972,10 +10993,10 @@
         <v>10</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>3486</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3485</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -10995,10 +11016,10 @@
         <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>3486</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3485</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -11018,10 +11039,10 @@
         <v>10</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>3487</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3486</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -11041,10 +11062,10 @@
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>3487</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3486</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -11064,10 +11085,10 @@
         <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>3485</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3484</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -11087,10 +11108,10 @@
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>3487</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3486</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -11110,10 +11131,10 @@
         <v>10</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>3488</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3487</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -11133,10 +11154,10 @@
         <v>10</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>3488</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3487</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -11156,10 +11177,10 @@
         <v>10</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>3488</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3487</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -11179,10 +11200,10 @@
         <v>10</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>3489</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3488</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -11202,10 +11223,10 @@
         <v>10</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>3485</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3484</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -11225,10 +11246,10 @@
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>3489</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <v>3488</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -11248,7 +11269,7 @@
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -11271,7 +11292,7 @@
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -11294,7 +11315,7 @@
         <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -11317,7 +11338,7 @@
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -11340,7 +11361,7 @@
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -11363,7 +11384,7 @@
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -11386,7 +11407,7 @@
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -11409,7 +11430,7 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -11432,7 +11453,7 @@
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -11455,7 +11476,7 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -11478,7 +11499,7 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -11501,7 +11522,7 @@
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -11524,7 +11545,7 @@
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
@@ -11547,7 +11568,7 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -11570,7 +11591,7 @@
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -11593,7 +11614,7 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
@@ -11616,7 +11637,7 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
@@ -11639,7 +11660,7 @@
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
@@ -11662,7 +11683,7 @@
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -11685,7 +11706,7 @@
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -11708,7 +11729,7 @@
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -11731,7 +11752,7 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -11754,7 +11775,7 @@
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
@@ -11777,7 +11798,7 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
@@ -11800,7 +11821,7 @@
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
@@ -11823,7 +11844,7 @@
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -11846,7 +11867,7 @@
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
@@ -11869,7 +11890,7 @@
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
@@ -11892,7 +11913,7 @@
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
@@ -11915,7 +11936,7 @@
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
@@ -11938,7 +11959,7 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
@@ -11961,7 +11982,7 @@
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
@@ -11984,7 +12005,7 @@
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
@@ -12007,7 +12028,7 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
@@ -12030,7 +12051,7 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
@@ -12053,7 +12074,7 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
@@ -12076,7 +12097,7 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
@@ -12099,7 +12120,7 @@
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
@@ -12122,7 +12143,7 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
@@ -12145,7 +12166,7 @@
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
@@ -12168,7 +12189,7 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
@@ -12191,7 +12212,7 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
@@ -12214,7 +12235,7 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
@@ -12237,7 +12258,7 @@
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
@@ -12260,7 +12281,7 @@
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
@@ -12283,7 +12304,7 @@
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
@@ -12306,7 +12327,7 @@
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
@@ -12329,7 +12350,7 @@
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
@@ -12352,7 +12373,7 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
@@ -12375,7 +12396,7 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -12398,7 +12419,7 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -12421,7 +12442,7 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -12444,7 +12465,7 @@
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -12467,7 +12488,7 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -12490,7 +12511,7 @@
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
@@ -12513,7 +12534,7 @@
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
@@ -12536,7 +12557,7 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
@@ -12559,7 +12580,7 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
@@ -12582,7 +12603,7 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
@@ -12605,7 +12626,7 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
@@ -12628,7 +12649,7 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
@@ -12651,7 +12672,7 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
@@ -12674,7 +12695,7 @@
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
@@ -12697,7 +12718,7 @@
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
@@ -12720,7 +12741,7 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
@@ -12743,7 +12764,7 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
@@ -12766,7 +12787,7 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
@@ -12789,7 +12810,7 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
@@ -12812,7 +12833,7 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
@@ -12835,7 +12856,7 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
@@ -12858,7 +12879,7 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
@@ -12881,7 +12902,7 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
@@ -12904,7 +12925,7 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
@@ -12927,7 +12948,7 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
@@ -12950,7 +12971,7 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
@@ -12973,7 +12994,7 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
@@ -12996,7 +13017,7 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
@@ -13019,7 +13040,7 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
@@ -13042,7 +13063,7 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
@@ -13065,7 +13086,7 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
@@ -13088,7 +13109,7 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
@@ -13111,7 +13132,7 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
@@ -13134,7 +13155,7 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
@@ -13157,7 +13178,7 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>3492</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
@@ -13180,7 +13201,7 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
@@ -13203,7 +13224,7 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
@@ -13226,7 +13247,7 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
@@ -13249,7 +13270,7 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
@@ -35193,7 +35214,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1201" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1201" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1201" t="s">
         <v>2775</v>
       </c>
@@ -35213,7 +35234,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1202" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1202" t="s">
         <v>2778</v>
       </c>
@@ -35233,7 +35254,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1203" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1203" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1203" t="s">
         <v>2781</v>
       </c>
@@ -35253,7 +35274,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1204" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1204" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1204" t="s">
         <v>2784</v>
       </c>
@@ -35273,7 +35294,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1205" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1205" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1205" t="s">
         <v>2787</v>
       </c>
@@ -35293,7 +35314,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1206" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1206" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1206" t="s">
         <v>2790</v>
       </c>
@@ -35313,7 +35334,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1207" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1207" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1207" t="s">
         <v>2793</v>
       </c>
@@ -35332,8 +35353,11 @@
       <c r="F1207" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="1208" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1207" t="s">
+        <v>3495</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1208" t="s">
         <v>2798</v>
       </c>
@@ -35352,8 +35376,11 @@
       <c r="F1208" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="1209" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1208" t="s">
+        <v>3496</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1209" t="s">
         <v>2801</v>
       </c>
@@ -35372,8 +35399,11 @@
       <c r="F1209" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="1210" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1209" t="s">
+        <v>3499</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1210" t="s">
         <v>2804</v>
       </c>
@@ -35392,8 +35422,11 @@
       <c r="F1210" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="1211" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1210" t="s">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1211" t="s">
         <v>2806</v>
       </c>
@@ -35412,8 +35445,11 @@
       <c r="F1211" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="1212" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1211" t="s">
+        <v>3501</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1212" t="s">
         <v>2809</v>
       </c>
@@ -35433,7 +35469,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="1213" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1213" t="s">
         <v>2812</v>
       </c>
@@ -35453,7 +35489,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1214" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1214" t="s">
         <v>2815</v>
       </c>
@@ -35473,7 +35509,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1215" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1215" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1215" t="s">
         <v>2818</v>
       </c>
@@ -35493,7 +35529,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1216" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1216" t="s">
         <v>2821</v>
       </c>
